--- a/docs/reference-forms/output/xlsx/TAI-FORM-REF-C007.xlsx
+++ b/docs/reference-forms/output/xlsx/TAI-FORM-REF-C007.xlsx
@@ -10,8 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안전보건 예산 편성 서식" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'안전보건 예산 편성 서식'!$A$2:$C$10</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'안전보건 예산 편성 서식'!$A$1:$D$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'안전보건 예산 편성 서식'!$A$1:$D$286</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,18 +46,12 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
       <i val="1"/>
       <color rgb="00000000"/>
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -77,12 +70,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00DCE6F1"/>
       </patternFill>
     </fill>
     <fill>
@@ -109,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -121,12 +109,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -203,6 +185,18 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_REF_C007_1" displayName="T_REF_C007_1" ref="A2:C62" headerRowCount="1">
+  <autoFilter ref="A2:C62"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="구분"/>
+    <tableColumn id="2" name="2021"/>
+    <tableColumn id="3" name="2022"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -494,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -526,255 +520,499 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="3" t="inlineStr"/>
       <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="3" t="inlineStr"/>
       <c r="B4" s="3" t="inlineStr"/>
       <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="3" t="inlineStr"/>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="3" t="inlineStr"/>
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="3" t="inlineStr"/>
       <c r="B6" s="3" t="inlineStr"/>
       <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="inlineStr"/>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="3" t="inlineStr"/>
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="3" t="inlineStr"/>
       <c r="B8" s="3" t="inlineStr"/>
       <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="3" t="inlineStr"/>
       <c r="B9" s="3" t="inlineStr"/>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="3" t="inlineStr"/>
       <c r="B10" s="3" t="inlineStr"/>
       <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="3" t="inlineStr"/>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>합계</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="3" t="inlineStr"/>
+      <c r="B12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="3" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="3" t="inlineStr"/>
+      <c r="B15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="3" t="inlineStr"/>
+      <c r="B16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="3" t="inlineStr"/>
+      <c r="B17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="3" t="inlineStr"/>
+      <c r="B18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="3" t="inlineStr"/>
+      <c r="B19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="3" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="3" t="inlineStr"/>
+      <c r="B21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="3" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="3" t="inlineStr"/>
+      <c r="B23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="3" t="inlineStr"/>
+      <c r="B24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="3" t="inlineStr"/>
+      <c r="B25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="3" t="inlineStr"/>
+      <c r="B26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="3" t="inlineStr"/>
+      <c r="B27" s="3" t="inlineStr"/>
+      <c r="C27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="3" t="inlineStr"/>
+      <c r="B28" s="3" t="inlineStr"/>
+      <c r="C28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="3" t="inlineStr"/>
+      <c r="B29" s="3" t="inlineStr"/>
+      <c r="C29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="3" t="inlineStr"/>
+      <c r="B30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="3" t="inlineStr"/>
+      <c r="B31" s="3" t="inlineStr"/>
+      <c r="C31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="3" t="inlineStr"/>
+      <c r="B32" s="3" t="inlineStr"/>
+      <c r="C32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="3" t="inlineStr"/>
+      <c r="B33" s="3" t="inlineStr"/>
+      <c r="C33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="3" t="inlineStr"/>
+      <c r="B34" s="3" t="inlineStr"/>
+      <c r="C34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="3" t="inlineStr"/>
+      <c r="B35" s="3" t="inlineStr"/>
+      <c r="C35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="3" t="inlineStr"/>
+      <c r="B36" s="3" t="inlineStr"/>
+      <c r="C36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="3" t="inlineStr"/>
+      <c r="B37" s="3" t="inlineStr"/>
+      <c r="C37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="3" t="inlineStr"/>
+      <c r="B38" s="3" t="inlineStr"/>
+      <c r="C38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="3" t="inlineStr"/>
+      <c r="B39" s="3" t="inlineStr"/>
+      <c r="C39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="3" t="inlineStr"/>
+      <c r="B40" s="3" t="inlineStr"/>
+      <c r="C40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="3" t="inlineStr"/>
+      <c r="B41" s="3" t="inlineStr"/>
+      <c r="C41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="3" t="inlineStr"/>
+      <c r="B42" s="3" t="inlineStr"/>
+      <c r="C42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="3" t="inlineStr"/>
+      <c r="B43" s="3" t="inlineStr"/>
+      <c r="C43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="3" t="inlineStr"/>
+      <c r="B44" s="3" t="inlineStr"/>
+      <c r="C44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="3" t="inlineStr"/>
+      <c r="B45" s="3" t="inlineStr"/>
+      <c r="C45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="3" t="inlineStr"/>
+      <c r="B46" s="3" t="inlineStr"/>
+      <c r="C46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="3" t="inlineStr"/>
+      <c r="B47" s="3" t="inlineStr"/>
+      <c r="C47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="3" t="inlineStr"/>
+      <c r="B48" s="3" t="inlineStr"/>
+      <c r="C48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="3" t="inlineStr"/>
+      <c r="B49" s="3" t="inlineStr"/>
+      <c r="C49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="3" t="inlineStr"/>
+      <c r="B50" s="3" t="inlineStr"/>
+      <c r="C50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="3" t="inlineStr"/>
+      <c r="B51" s="3" t="inlineStr"/>
+      <c r="C51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="3" t="inlineStr"/>
+      <c r="B52" s="3" t="inlineStr"/>
+      <c r="C52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="3" t="inlineStr"/>
+      <c r="B53" s="3" t="inlineStr"/>
+      <c r="C53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="3" t="inlineStr"/>
+      <c r="B54" s="3" t="inlineStr"/>
+      <c r="C54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="3" t="inlineStr"/>
+      <c r="B55" s="3" t="inlineStr"/>
+      <c r="C55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="3" t="inlineStr"/>
+      <c r="B56" s="3" t="inlineStr"/>
+      <c r="C56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="3" t="inlineStr"/>
+      <c r="B57" s="3" t="inlineStr"/>
+      <c r="C57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="3" t="inlineStr"/>
+      <c r="B58" s="3" t="inlineStr"/>
+      <c r="C58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="3" t="inlineStr"/>
+      <c r="B59" s="3" t="inlineStr"/>
+      <c r="C59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="3" t="inlineStr"/>
+      <c r="B60" s="3" t="inlineStr"/>
+      <c r="C60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="3" t="inlineStr"/>
+      <c r="B61" s="3" t="inlineStr"/>
+      <c r="C61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="3" t="inlineStr"/>
+      <c r="B62" s="3" t="inlineStr"/>
+      <c r="C62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63" ht="28" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>【예산 편성항목 예시】 (원본 HWP-07, 단위: 백만원)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>인력 및 시설분야</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="65" ht="28" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  · 위험시설 정비 및 개보수</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="66" ht="28" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  · 안전검사 실시</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="67" ht="28" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  · 안전시설 신규 설치 및 투자</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="68" ht="28" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  · 안전보건조직 노무관리</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
         <is>
           <t>안전분야</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="70" ht="28" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  · 안전인력 육성 및 교육</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="71" ht="28" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  · 안전보건 진단 및 컨설팅</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="72" ht="28" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  · 위험성평가 실시</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="73" ht="28" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  · 안전보호구 구입</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="74" ht="28" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>보건분야</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="75" ht="28" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  · 작업환경측정 실시</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="76" ht="28" customHeight="1">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  · 특수건강검진 실시</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="77" ht="28" customHeight="1">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  · 근골격계질환 예방</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="78" ht="28" customHeight="1">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  · 휴게‧위생시설 관리</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="79" ht="28" customHeight="1">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="80" ht="28" customHeight="1">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  · 협력사 안전관리 역량 지원</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="81" ht="28" customHeight="1">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">    - 교육 지원</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="82" ht="28" customHeight="1">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">    - 시설 지원</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="83" ht="28" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  · 안전보건 캠페인 추진</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="84" ht="28" customHeight="1">
+      <c r="A84" s="4" t="inlineStr">
         <is>
           <t>예비비</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
+    <row r="85" ht="28" customHeight="1">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  · 예비비</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C10"/>
   <mergeCells count="24">
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A72:D72"/>
+    <mergeCell ref="A81:D81"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="A77:D77"/>
+    <mergeCell ref="A83:D83"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A82:D82"/>
+    <mergeCell ref="A73:D73"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A79:D79"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A78:D78"/>
+    <mergeCell ref="A65:D65"/>
+    <mergeCell ref="A84:D84"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A80:D80"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A85:D85"/>
+    <mergeCell ref="A76:D76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/docs/reference-forms/output/xlsx/TAI-FORM-REF-C007.xlsx
+++ b/docs/reference-forms/output/xlsx/TAI-FORM-REF-C007.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안전보건 예산 편성 서식" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'안전보건 예산 편성 서식'!$A$1:$D$286</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'안전보건 예산 편성 서식'!$A$1:$D$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
